--- a/Datasets/Advanced Analysis Experiments/30_models_ISA_score_3_different_system_prompt.xlsx
+++ b/Datasets/Advanced Analysis Experiments/30_models_ISA_score_3_different_system_prompt.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.992592592592593</v>
+        <v>2.072222222222222</v>
       </c>
       <c r="C2" t="n">
-        <v>2.635185185185185</v>
+        <v>2.659259259259259</v>
       </c>
       <c r="D2" t="n">
         <v>2.038888888888889</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.068518518518518</v>
+        <v>2.212962962962963</v>
       </c>
       <c r="C4" t="n">
-        <v>2.746296296296296</v>
+        <v>2.840740740740741</v>
       </c>
       <c r="D4" t="n">
         <v>2.135185185185185</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.722222222222222</v>
+        <v>1.644444444444444</v>
       </c>
       <c r="C5" t="n">
-        <v>2.035185185185185</v>
+        <v>2.075925925925926</v>
       </c>
       <c r="D5" t="n">
         <v>1.746296296296296</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.07962962962963</v>
+        <v>1.981481481481482</v>
       </c>
       <c r="C7" t="n">
-        <v>2.574074074074074</v>
+        <v>2.542592592592593</v>
       </c>
       <c r="D7" t="n">
         <v>2.083333333333333</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.885185185185185</v>
+        <v>1.87037037037037</v>
       </c>
       <c r="C10" t="n">
-        <v>2.222222222222222</v>
+        <v>2.209259259259259</v>
       </c>
       <c r="D10" t="n">
         <v>1.888888888888889</v>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.490740740740741</v>
+        <v>1.461111111111111</v>
       </c>
       <c r="C11" t="n">
-        <v>1.946296296296296</v>
+        <v>1.877777777777778</v>
       </c>
       <c r="D11" t="n">
         <v>1.375925925925926</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.214814814814815</v>
+        <v>2.181481481481482</v>
       </c>
       <c r="C13" t="n">
-        <v>2.57037037037037</v>
+        <v>2.457407407407407</v>
       </c>
       <c r="D13" t="n">
         <v>2.111111111111111</v>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.312962962962963</v>
+        <v>2.361111111111111</v>
       </c>
       <c r="C14" t="n">
-        <v>2.675925925925926</v>
+        <v>2.683333333333333</v>
       </c>
       <c r="D14" t="n">
         <v>2.235185185185185</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.970370370370371</v>
+        <v>2.033333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>2.492592592592593</v>
+        <v>2.446296296296296</v>
       </c>
       <c r="D16" t="n">
         <v>1.840740740740741</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.557407407407407</v>
+        <v>1.487037037037037</v>
       </c>
       <c r="C17" t="n">
-        <v>1.442592592592592</v>
+        <v>1.414814814814815</v>
       </c>
       <c r="D17" t="n">
         <v>1.559259259259259</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.118518518518519</v>
+        <v>2.183333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>2.692592592592593</v>
+        <v>2.733333333333333</v>
       </c>
       <c r="D18" t="n">
         <v>1.888888888888889</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.609259259259259</v>
+        <v>1.527777777777778</v>
       </c>
       <c r="C19" t="n">
-        <v>2.518518518518519</v>
+        <v>2.47037037037037</v>
       </c>
       <c r="D19" t="n">
         <v>1.609259259259259</v>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.844444444444445</v>
+        <v>1.698148148148148</v>
       </c>
       <c r="C20" t="n">
-        <v>2.077777777777778</v>
+        <v>2.061111111111111</v>
       </c>
       <c r="D20" t="n">
         <v>1.748148148148148</v>
@@ -752,17 +752,17 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Llama-4-Scout</t>
+          <t>Llama-4-Maverick</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.688888888888889</v>
+        <v>1.801851851851852</v>
       </c>
       <c r="C21" t="n">
-        <v>2.105555555555556</v>
+        <v>1.9</v>
       </c>
       <c r="D21" t="n">
-        <v>1.507407407407407</v>
+        <v>1.907407407407408</v>
       </c>
     </row>
     <row r="22">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.755555555555556</v>
+        <v>1.688888888888889</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>2.105555555555556</v>
       </c>
       <c r="D22" t="n">
         <v>1.507407407407407</v>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.816666666666667</v>
+        <v>1.835185185185185</v>
       </c>
       <c r="C23" t="n">
-        <v>2.624074074074074</v>
+        <v>2.674074074074074</v>
       </c>
       <c r="D23" t="n">
         <v>1.675925925925926</v>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.509259259259259</v>
+        <v>1.488888888888889</v>
       </c>
       <c r="C25" t="n">
-        <v>2.337037037037037</v>
+        <v>2.412962962962963</v>
       </c>
       <c r="D25" t="n">
         <v>1.416666666666667</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.648148148148148</v>
+        <v>1.644444444444445</v>
       </c>
       <c r="C26" t="n">
-        <v>2.085185185185185</v>
+        <v>2.066666666666667</v>
       </c>
       <c r="D26" t="n">
         <v>1.737037037037037</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.718518518518519</v>
+        <v>1.531481481481481</v>
       </c>
       <c r="C28" t="n">
-        <v>1.546296296296296</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D28" t="n">
         <v>1.733333333333333</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.411111111111111</v>
+        <v>1.522222222222222</v>
       </c>
       <c r="C30" t="n">
-        <v>2.207407407407407</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D30" t="n">
         <v>1.442592592592592</v>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.746296296296296</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="C31" t="n">
-        <v>2.388888888888889</v>
+        <v>2.401851851851852</v>
       </c>
       <c r="D31" t="n">
         <v>1.661111111111111</v>
